--- a/owlcms/src/main/resources/templates/cards/Card-A4.xlsx
+++ b/owlcms/src/main/resources/templates/cards/Card-A4.xlsx
@@ -72,7 +72,7 @@
     <t>${competition.competitionName} / ${competition.competitionCity}</t>
   </si>
   <si>
-    <t>Signature:</t>
+    <t>${t.get("Jury.Signature")}:</t>
   </si>
   <si>
     <t>${athlete.fullName}</t>
